--- a/sen_alpha/IGD_alpha.xlsx
+++ b/sen_alpha/IGD_alpha.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\代码\MOEA\Platemohjp\PlatEMO-master\PlatEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\论文\MOPSO_PPHS\1.experiments\sen_alpha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE94484-9BED-4036-A916-E5390419A044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFC7D04-45A6-4C05-9A0C-1F607B40ABB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="3150" windowWidth="19200" windowHeight="10050" xr2:uid="{2DFCC658-BD0C-47A7-B266-46F10D7575A5}"/>
+    <workbookView xWindow="1515" yWindow="1605" windowWidth="19200" windowHeight="10050" xr2:uid="{2DFCC658-BD0C-47A7-B266-46F10D7575A5}"/>
   </bookViews>
   <sheets>
     <sheet name="myIGD" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="171">
   <si>
     <t>Problem</t>
   </si>
@@ -48,24 +48,6 @@
   </si>
   <si>
     <t>D</t>
-  </si>
-  <si>
-    <t>alpha00</t>
-  </si>
-  <si>
-    <t>alpha01</t>
-  </si>
-  <si>
-    <t>alpha03</t>
-  </si>
-  <si>
-    <t>alpha05</t>
-  </si>
-  <si>
-    <t>alpha07</t>
-  </si>
-  <si>
-    <t>alpha10</t>
   </si>
   <si>
     <t>MOPSO_PPHS0</t>
@@ -642,7 +624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -658,6 +640,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -992,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9CC37BC-5CAC-4D4D-9D26-36A36AB04ABD}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -1010,31 +993,31 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="1">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="F1" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="I1" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1043,30 +1026,30 @@
         <v>10367</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1075,30 +1058,30 @@
         <v>7129</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1107,30 +1090,30 @@
         <v>2000</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1139,30 +1122,30 @@
         <v>7130</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1171,30 +1154,30 @@
         <v>5327</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -1203,30 +1186,30 @@
         <v>11225</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -1235,30 +1218,30 @@
         <v>10509</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -1267,30 +1250,30 @@
         <v>2308</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -1299,30 +1282,30 @@
         <v>12533</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -1331,30 +1314,30 @@
         <v>24526</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
@@ -1363,30 +1346,30 @@
         <v>22277</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
@@ -1395,30 +1378,30 @@
         <v>22277</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
@@ -1427,30 +1410,30 @@
         <v>22283</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
@@ -1459,30 +1442,30 @@
         <v>22283</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -1491,30 +1474,30 @@
         <v>29148</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -1523,30 +1506,30 @@
         <v>22283</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -1555,30 +1538,30 @@
         <v>22283</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -1587,30 +1570,30 @@
         <v>12625</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
@@ -1619,30 +1602,30 @@
         <v>12620</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -1651,53 +1634,76 @@
         <v>12646</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="G22" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="H22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>176</v>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D23" s="5">
+        <v>4.4749999999999996</v>
+      </c>
+      <c r="E23" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="F23" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="G23" s="5">
+        <v>4.3250000000000002</v>
+      </c>
+      <c r="H23" s="5">
+        <v>4.2</v>
+      </c>
+      <c r="I23" s="5">
+        <v>4.45</v>
+      </c>
+      <c r="J23">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
